--- a/data_generation/10_aquatic_toxicity/copper_aquatic_toxicity.xlsx
+++ b/data_generation/10_aquatic_toxicity/copper_aquatic_toxicity.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\aquatic_toxicity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\10_aquatic_toxicity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60065301-16E2-4F54-AFB3-F86C43BB03DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D147D9-91F3-4F21-BEDD-C3E10A1EA834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="aquatic_endpoints" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">aquatic_endpoints!$A$1:$V$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">aquatic_endpoints!$A$1:$W$123</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="147">
   <si>
     <t>Oncorhynchus mykiss</t>
   </si>
@@ -420,9 +420,6 @@
     <t>Cupric ion</t>
   </si>
   <si>
-    <t>Expressed as copper</t>
-  </si>
-  <si>
     <t>Early life stages, arithmetic means (see RAR B9)</t>
   </si>
   <si>
@@ -477,7 +474,13 @@
     <t>survival, autotomy, reproduction and total growth rate</t>
   </si>
   <si>
-    <t>Expressed as copper, duration of 187 d confirmed in the RAR from 2017, Vol B9, p. 124</t>
+    <t>expressed_as</t>
+  </si>
+  <si>
+    <t>duration of 187 d confirmed in the RAR from 2017, Vol B9, p. 124</t>
+  </si>
+  <si>
+    <t>Copper</t>
   </si>
 </sst>
 </file>
@@ -843,32 +846,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C316ADCA-0F97-4E34-A600-B1604EAF90B0}">
-  <dimension ref="A1:V124"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:W124"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.54296875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="22.453125" customWidth="1"/>
-    <col min="3" max="3" width="22.81640625" customWidth="1"/>
-    <col min="4" max="4" width="7.26953125" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="7.7265625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="6.54296875" customWidth="1"/>
-    <col min="8" max="8" width="5.54296875" style="9" customWidth="1"/>
-    <col min="9" max="9" width="17.81640625" customWidth="1"/>
-    <col min="10" max="10" width="17.26953125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="8.1796875" customWidth="1"/>
-    <col min="12" max="12" width="5.26953125" customWidth="1"/>
-    <col min="13" max="13" width="10.1796875" customWidth="1"/>
-    <col min="14" max="14" width="7.453125" customWidth="1"/>
-    <col min="15" max="15" width="14.26953125" customWidth="1"/>
-    <col min="16" max="16" width="22" customWidth="1"/>
-    <col min="17" max="17" width="5.7265625" customWidth="1"/>
-    <col min="18" max="18" width="9.54296875" customWidth="1"/>
-    <col min="19" max="19" width="16.453125" customWidth="1"/>
-    <col min="20" max="20" width="31.26953125" customWidth="1"/>
+    <col min="6" max="6" width="7.7109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.5703125" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" style="9" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" style="12" customWidth="1"/>
+    <col min="11" max="11" width="8.140625" customWidth="1"/>
+    <col min="12" max="12" width="5.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" customWidth="1"/>
+    <col min="14" max="14" width="7.42578125" customWidth="1"/>
+    <col min="15" max="15" width="7.42578125" style="12" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="5.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.5703125" customWidth="1"/>
+    <col min="20" max="20" width="16.42578125" customWidth="1"/>
+    <col min="21" max="21" width="31.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="10" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>104</v>
       </c>
@@ -912,31 +916,34 @@
         <v>17</v>
       </c>
       <c r="O1" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="P1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="Q1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="R1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="S1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="T1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="U1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="V1" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="W1" s="11" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>122</v>
       </c>
@@ -974,31 +981,32 @@
         <v>21</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R2" s="2">
         <v>80</v>
       </c>
-      <c r="R2" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" s="4"/>
       <c r="V2" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>125</v>
       </c>
@@ -1035,30 +1043,31 @@
       <c r="N3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="2"/>
+      <c r="P3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R3" s="2">
         <v>80</v>
       </c>
-      <c r="R3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T3" s="4"/>
-      <c r="U3" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="S3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U3" s="4"/>
+      <c r="V3" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>43</v>
       </c>
@@ -1094,31 +1103,32 @@
         <v>21</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R4" s="2">
         <v>80</v>
       </c>
-      <c r="R4" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U4" s="4"/>
       <c r="V4" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>125</v>
       </c>
@@ -1155,30 +1165,31 @@
       <c r="N5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="O5" s="2"/>
+      <c r="P5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R5" s="2">
         <v>80</v>
       </c>
-      <c r="R5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T5" s="4"/>
-      <c r="U5" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U5" s="4"/>
       <c r="V5" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>125</v>
       </c>
@@ -1192,7 +1203,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
@@ -1215,30 +1226,31 @@
       <c r="N6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O6" s="2"/>
+      <c r="P6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R6" s="2">
         <v>80</v>
       </c>
-      <c r="R6" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T6" s="4"/>
-      <c r="U6" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U6" s="4"/>
       <c r="V6" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
@@ -1276,31 +1288,32 @@
         <v>21</v>
       </c>
       <c r="O7" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R7" s="2">
         <v>80</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T7" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U7" s="4"/>
       <c r="V7" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>125</v>
       </c>
@@ -1337,30 +1350,31 @@
       <c r="N8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="O8" s="2"/>
+      <c r="P8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R8" s="2">
         <v>80</v>
       </c>
-      <c r="R8" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T8" s="4"/>
-      <c r="U8" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U8" s="4"/>
       <c r="V8" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
@@ -1372,7 +1386,7 @@
         <v>5</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
@@ -1396,31 +1410,32 @@
         <v>21</v>
       </c>
       <c r="O9" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R9" s="2">
         <v>80</v>
       </c>
-      <c r="R9" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T9" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U9" s="4"/>
       <c r="V9" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>125</v>
       </c>
@@ -1434,7 +1449,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
@@ -1457,30 +1472,31 @@
       <c r="N10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="O10" s="2"/>
+      <c r="P10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R10" s="2">
         <v>80</v>
       </c>
-      <c r="R10" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U10" s="2"/>
       <c r="V10" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
@@ -1492,7 +1508,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
@@ -1516,31 +1532,32 @@
         <v>21</v>
       </c>
       <c r="O11" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R11" s="2">
         <v>80</v>
       </c>
-      <c r="R11" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S11" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U11" s="2"/>
       <c r="V11" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>45</v>
       </c>
@@ -1554,7 +1571,7 @@
         <v>7</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
@@ -1578,31 +1595,32 @@
         <v>21</v>
       </c>
       <c r="O12" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R12" s="2">
         <v>80</v>
       </c>
-      <c r="R12" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S12" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U12" s="2"/>
       <c r="V12" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>52</v>
       </c>
@@ -1616,7 +1634,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
@@ -1640,31 +1658,32 @@
         <v>21</v>
       </c>
       <c r="O13" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R13" s="2">
         <v>80</v>
       </c>
-      <c r="R13" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S13" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U13" s="2"/>
       <c r="V13" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>52</v>
       </c>
@@ -1702,33 +1721,34 @@
         <v>21</v>
       </c>
       <c r="O14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R14" s="2">
         <v>80</v>
       </c>
-      <c r="R14" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S14" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U14" s="2"/>
       <c r="V14" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
@@ -1762,36 +1782,37 @@
         <v>21</v>
       </c>
       <c r="O15" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R15" s="2">
         <v>80</v>
       </c>
-      <c r="R15" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S15" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U15" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U15" s="2"/>
       <c r="V15" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>125</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>0</v>
@@ -1823,32 +1844,33 @@
       <c r="N16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="O16" s="2"/>
+      <c r="P16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P16" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R16" s="2">
         <v>80</v>
       </c>
-      <c r="R16" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>48</v>
@@ -1884,31 +1906,32 @@
         <v>21</v>
       </c>
       <c r="O17" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P17" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R17" s="2">
         <v>80</v>
       </c>
-      <c r="R17" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S17" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U17" s="2"/>
       <c r="V17" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>125</v>
       </c>
@@ -1945,32 +1968,33 @@
       <c r="N18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="O18" s="2"/>
+      <c r="P18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P18" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R18" s="2">
         <v>80</v>
       </c>
-      <c r="R18" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T18" s="13"/>
-      <c r="U18" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U18" s="14"/>
       <c r="V18" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
@@ -1982,7 +2006,7 @@
         <v>12</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
@@ -2006,31 +2030,32 @@
         <v>21</v>
       </c>
       <c r="O19" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P19" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R19" s="2">
         <v>80</v>
       </c>
-      <c r="R19" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S19" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U19" s="2"/>
       <c r="V19" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>122</v>
       </c>
@@ -2049,7 +2074,7 @@
         <v>84</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>39</v>
@@ -2068,31 +2093,32 @@
         <v>21</v>
       </c>
       <c r="O20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P20" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R20" s="2">
         <v>80</v>
       </c>
-      <c r="R20" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S20" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U20" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U20" s="2"/>
       <c r="V20" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>125</v>
       </c>
@@ -2111,7 +2137,7 @@
         <v>84</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>39</v>
@@ -2129,30 +2155,31 @@
       <c r="N21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="O21" s="2"/>
+      <c r="P21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R21" s="2">
         <v>80</v>
       </c>
-      <c r="R21" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T21" s="13"/>
-      <c r="U21" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U21" s="14"/>
       <c r="V21" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>52</v>
       </c>
@@ -2190,31 +2217,32 @@
         <v>21</v>
       </c>
       <c r="O22" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P22" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R22" s="2">
         <v>80</v>
       </c>
-      <c r="R22" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S22" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U22" s="2"/>
       <c r="V22" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>122</v>
       </c>
@@ -2228,10 +2256,10 @@
         <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>28</v>
@@ -2254,31 +2282,32 @@
         <v>21</v>
       </c>
       <c r="O23" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P23" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R23" s="2">
         <v>81</v>
       </c>
-      <c r="R23" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S23" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U23" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U23" s="2"/>
       <c r="V23" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>125</v>
       </c>
@@ -2292,10 +2321,10 @@
         <v>15</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>28</v>
@@ -2317,49 +2346,50 @@
       <c r="N24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="O24" s="2"/>
+      <c r="P24" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P24" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R24" s="2">
         <v>81</v>
       </c>
-      <c r="R24" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T24" s="13"/>
-      <c r="U24" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U24" s="14"/>
       <c r="V24" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D25" s="2">
         <v>16</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>38</v>
@@ -2378,50 +2408,51 @@
         <v>21</v>
       </c>
       <c r="O25" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P25" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R25" s="2">
         <v>81</v>
       </c>
-      <c r="R25" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S25" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U25" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U25" s="2"/>
       <c r="V25" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>43</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D26" s="2">
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>38</v>
@@ -2440,50 +2471,51 @@
         <v>21</v>
       </c>
       <c r="O26" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P26" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P26" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R26" s="2">
         <v>81</v>
       </c>
-      <c r="R26" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S26" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U26" s="2"/>
       <c r="V26" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W26" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D27" s="2">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>38</v>
@@ -2502,50 +2534,51 @@
         <v>21</v>
       </c>
       <c r="O27" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P27" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P27" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R27" s="2">
         <v>81</v>
       </c>
-      <c r="R27" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S27" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U27" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U27" s="2"/>
       <c r="V27" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D28" s="2">
         <v>19</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>38</v>
@@ -2564,50 +2597,51 @@
         <v>21</v>
       </c>
       <c r="O28" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P28" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R28" s="2">
         <v>81</v>
       </c>
-      <c r="R28" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S28" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U28" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U28" s="2"/>
       <c r="V28" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D29" s="2">
         <v>20</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>38</v>
@@ -2626,36 +2660,37 @@
         <v>21</v>
       </c>
       <c r="O29" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P29" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R29" s="2">
         <v>81</v>
       </c>
-      <c r="R29" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S29" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U29" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U29" s="2"/>
       <c r="V29" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>2</v>
@@ -2672,7 +2707,7 @@
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>53</v>
@@ -2690,29 +2725,30 @@
         <v>21</v>
       </c>
       <c r="O30" s="2"/>
-      <c r="P30" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q30" s="2">
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R30" s="2">
         <v>82</v>
       </c>
-      <c r="R30" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T30" s="2"/>
-      <c r="U30" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U30" s="2"/>
       <c r="V30" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W30" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
@@ -2745,32 +2781,33 @@
       <c r="N31" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q31" s="2">
+      <c r="O31" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R31" s="2">
         <v>82</v>
       </c>
-      <c r="R31" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S31" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U31" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U31" s="2"/>
       <c r="V31" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W31" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
@@ -2803,32 +2840,33 @@
       <c r="N32" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q32" s="2">
+      <c r="O32" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R32" s="2">
         <v>82</v>
       </c>
-      <c r="R32" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S32" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U32" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U32" s="2"/>
       <c r="V32" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
@@ -2861,32 +2899,33 @@
       <c r="N33" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O33" s="2"/>
-      <c r="P33" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q33" s="2">
+      <c r="O33" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R33" s="2">
         <v>82</v>
       </c>
-      <c r="R33" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S33" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U33" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U33" s="2"/>
       <c r="V33" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
@@ -2904,7 +2943,7 @@
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>56</v>
@@ -2921,32 +2960,33 @@
       <c r="N34" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q34" s="2">
+      <c r="O34" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R34" s="2">
         <v>82</v>
       </c>
-      <c r="R34" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S34" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U34" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U34" s="2"/>
       <c r="V34" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
@@ -2979,32 +3019,33 @@
       <c r="N35" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O35" s="2"/>
-      <c r="P35" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q35" s="2">
+      <c r="O35" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R35" s="2">
         <v>82</v>
       </c>
-      <c r="R35" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S35" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U35" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U35" s="2"/>
       <c r="V35" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2" t="s">
@@ -3037,32 +3078,33 @@
       <c r="N36" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O36" s="2"/>
-      <c r="P36" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q36" s="2">
+      <c r="O36" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R36" s="2">
         <v>82</v>
       </c>
-      <c r="R36" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S36" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U36" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U36" s="2"/>
       <c r="V36" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W36" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
@@ -3080,7 +3122,7 @@
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>53</v>
@@ -3097,32 +3139,33 @@
       <c r="N37" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O37" s="2"/>
-      <c r="P37" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q37" s="2">
+      <c r="O37" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R37" s="2">
         <v>82</v>
       </c>
-      <c r="R37" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S37" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U37" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U37" s="2"/>
       <c r="V37" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W37" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
@@ -3140,7 +3183,7 @@
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>56</v>
@@ -3157,32 +3200,33 @@
       <c r="N38" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q38" s="2">
+      <c r="O38" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R38" s="2">
         <v>82</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S38" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U38" s="2"/>
       <c r="V38" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
@@ -3200,7 +3244,7 @@
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>56</v>
@@ -3217,32 +3261,33 @@
       <c r="N39" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O39" s="2"/>
-      <c r="P39" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q39" s="2">
+      <c r="O39" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R39" s="2">
         <v>82</v>
       </c>
-      <c r="R39" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S39" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U39" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U39" s="2"/>
       <c r="V39" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W39" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2" t="s">
@@ -3275,32 +3320,33 @@
       <c r="N40" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O40" s="2"/>
-      <c r="P40" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q40" s="2">
+      <c r="O40" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R40" s="2">
         <v>82</v>
       </c>
-      <c r="R40" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S40" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U40" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U40" s="2"/>
       <c r="V40" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W40" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2" t="s">
@@ -3318,7 +3364,7 @@
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>58</v>
@@ -3335,30 +3381,31 @@
       <c r="N41" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O41" s="2"/>
-      <c r="P41" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q41" s="2">
+      <c r="O41" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R41" s="2">
         <v>82</v>
       </c>
-      <c r="R41" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S41" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U41" s="2" t="s">
-        <v>113</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U41" s="2"/>
       <c r="V41" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="W41" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>125</v>
       </c>
@@ -3377,7 +3424,7 @@
         <v>93</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>40</v>
@@ -3395,32 +3442,33 @@
       <c r="N42" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="O42" s="7" t="s">
+      <c r="O42" s="7"/>
+      <c r="P42" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="P42" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q42" s="7">
+      <c r="Q42" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="R42" s="7">
         <v>82</v>
       </c>
-      <c r="R42" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S42" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T42" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="U42" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V42" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U42" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W42" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>125</v>
       </c>
@@ -3439,7 +3487,7 @@
         <v>93</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I43" s="7" t="s">
         <v>38</v>
@@ -3457,32 +3505,33 @@
       <c r="N43" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="O43" s="7" t="s">
+      <c r="O43" s="7"/>
+      <c r="P43" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="P43" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q43" s="7">
+      <c r="Q43" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="R43" s="7">
         <v>82</v>
       </c>
-      <c r="R43" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S43" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T43" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="U43" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V43" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U43" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W43" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>125</v>
       </c>
@@ -3518,29 +3567,30 @@
         <v>21</v>
       </c>
       <c r="O44" s="7"/>
-      <c r="P44" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q44" s="7">
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="R44" s="7">
         <v>82</v>
       </c>
-      <c r="R44" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T44" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="U44" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V44" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U44" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W44" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>125</v>
       </c>
@@ -3576,31 +3626,32 @@
         <v>21</v>
       </c>
       <c r="O45" s="2"/>
-      <c r="P45" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q45" s="2">
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R45" s="2">
         <v>82</v>
       </c>
-      <c r="R45" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T45" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="U45" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V45" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U45" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="V45" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W45" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2" t="s">
@@ -3614,13 +3665,17 @@
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H46" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>140</v>
+      </c>
       <c r="I46" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J46" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="K46" s="2" t="s">
         <v>6</v>
       </c>
@@ -3628,37 +3683,38 @@
         <v>33</v>
       </c>
       <c r="M46" s="2">
-        <v>5.9499999999999997E-2</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q46" s="2">
+      <c r="O46" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R46" s="2">
         <v>83</v>
       </c>
-      <c r="R46" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S46" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="U46" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V46" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U46" s="2"/>
+      <c r="V46" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W46" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2" t="s">
@@ -3672,13 +3728,13 @@
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="H47" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I47" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>60</v>
@@ -3690,37 +3746,38 @@
         <v>33</v>
       </c>
       <c r="M47" s="2">
-        <v>1.6500000000000001E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O47" s="2"/>
-      <c r="P47" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q47" s="2">
+      <c r="O47" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R47" s="2">
         <v>83</v>
       </c>
-      <c r="R47" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S47" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U47" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V47" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U47" s="2"/>
+      <c r="V47" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W47" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2" t="s">
@@ -3734,13 +3791,13 @@
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H48" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I48" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>60</v>
@@ -3752,37 +3809,38 @@
         <v>33</v>
       </c>
       <c r="M48" s="2">
-        <v>2.3E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O48" s="2"/>
-      <c r="P48" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q48" s="2">
+      <c r="O48" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R48" s="2">
         <v>83</v>
       </c>
-      <c r="R48" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S48" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U48" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V48" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U48" s="2"/>
+      <c r="V48" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W48" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2" t="s">
@@ -3798,15 +3856,11 @@
       <c r="G49" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H49" s="2" t="s">
-        <v>141</v>
-      </c>
+      <c r="H49" s="2"/>
       <c r="I49" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>60</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
         <v>6</v>
       </c>
@@ -3814,37 +3868,40 @@
         <v>33</v>
       </c>
       <c r="M49" s="2">
-        <v>1.6E-2</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O49" s="2"/>
-      <c r="P49" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q49" s="2">
+      <c r="O49" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R49" s="2">
         <v>83</v>
       </c>
-      <c r="R49" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S49" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="U49" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V49" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+      <c r="V49" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W49" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2" t="s">
@@ -3862,7 +3919,7 @@
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>56</v>
@@ -3879,32 +3936,33 @@
       <c r="N50" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O50" s="2"/>
-      <c r="P50" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q50" s="2">
+      <c r="O50" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R50" s="2">
         <v>83</v>
       </c>
-      <c r="R50" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S50" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U50" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V50" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U50" s="2"/>
+      <c r="V50" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W50" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2" t="s">
@@ -3939,32 +3997,33 @@
       <c r="N51" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O51" s="2"/>
-      <c r="P51" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q51" s="2">
+      <c r="O51" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R51" s="2">
         <v>83</v>
       </c>
-      <c r="R51" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S51" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U51" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V51" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U51" s="2"/>
+      <c r="V51" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W51" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2" t="s">
@@ -3984,7 +4043,7 @@
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>56</v>
@@ -4001,32 +4060,33 @@
       <c r="N52" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O52" s="2"/>
-      <c r="P52" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q52" s="2">
+      <c r="O52" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R52" s="2">
         <v>83</v>
       </c>
-      <c r="R52" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S52" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U52" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V52" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U52" s="2"/>
+      <c r="V52" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W52" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2" t="s">
@@ -4059,32 +4119,33 @@
       <c r="N53" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O53" s="2"/>
-      <c r="P53" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q53" s="2">
+      <c r="O53" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R53" s="2">
         <v>83</v>
       </c>
-      <c r="R53" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S53" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T53" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U53" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V53" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U53" s="2"/>
+      <c r="V53" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W53" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2" t="s">
@@ -4117,32 +4178,33 @@
       <c r="N54" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O54" s="2"/>
-      <c r="P54" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q54" s="2">
+      <c r="O54" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R54" s="2">
         <v>83</v>
       </c>
-      <c r="R54" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S54" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T54" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U54" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V54" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U54" s="2"/>
+      <c r="V54" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W54" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2" t="s">
@@ -4175,32 +4237,33 @@
       <c r="N55" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O55" s="2"/>
-      <c r="P55" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q55" s="2">
+      <c r="O55" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R55" s="2">
         <v>83</v>
       </c>
-      <c r="R55" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S55" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T55" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U55" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V55" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U55" s="2"/>
+      <c r="V55" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W55" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2" t="s">
@@ -4233,32 +4296,33 @@
       <c r="N56" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O56" s="2"/>
-      <c r="P56" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q56" s="2">
+      <c r="O56" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R56" s="2">
         <v>83</v>
       </c>
-      <c r="R56" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S56" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T56" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U56" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V56" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U56" s="2"/>
+      <c r="V56" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W56" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2" t="s">
@@ -4293,32 +4357,33 @@
       <c r="N57" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O57" s="2"/>
-      <c r="P57" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q57" s="2">
+      <c r="O57" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R57" s="2">
         <v>83</v>
       </c>
-      <c r="R57" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S57" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T57" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U57" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V57" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U57" s="2"/>
+      <c r="V57" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W57" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2" t="s">
@@ -4336,7 +4401,7 @@
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>64</v>
@@ -4353,32 +4418,33 @@
       <c r="N58" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O58" s="2"/>
-      <c r="P58" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q58" s="2">
+      <c r="O58" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R58" s="2">
         <v>83</v>
       </c>
-      <c r="R58" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S58" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U58" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V58" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U58" s="2"/>
+      <c r="V58" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W58" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="2" t="s">
@@ -4396,7 +4462,7 @@
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>64</v>
@@ -4413,32 +4479,33 @@
       <c r="N59" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O59" s="2"/>
-      <c r="P59" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q59" s="2">
+      <c r="O59" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R59" s="2">
         <v>83</v>
       </c>
-      <c r="R59" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S59" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U59" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V59" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U59" s="2"/>
+      <c r="V59" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W59" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" s="2" t="s">
@@ -4456,7 +4523,7 @@
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>64</v>
@@ -4473,32 +4540,33 @@
       <c r="N60" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O60" s="2"/>
-      <c r="P60" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q60" s="2">
+      <c r="O60" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R60" s="2">
         <v>83</v>
       </c>
-      <c r="R60" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S60" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U60" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V60" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U60" s="2"/>
+      <c r="V60" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W60" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2" t="s">
@@ -4516,7 +4584,7 @@
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>64</v>
@@ -4533,32 +4601,33 @@
       <c r="N61" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O61" s="2"/>
-      <c r="P61" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q61" s="2">
+      <c r="O61" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R61" s="2">
         <v>83</v>
       </c>
-      <c r="R61" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S61" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U61" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V61" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U61" s="2"/>
+      <c r="V61" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W61" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2" t="s">
@@ -4576,7 +4645,7 @@
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>64</v>
@@ -4593,35 +4662,36 @@
       <c r="N62" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O62" s="2"/>
-      <c r="P62" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q62" s="2">
+      <c r="O62" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R62" s="2">
         <v>83</v>
       </c>
-      <c r="R62" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S62" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U62" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V62" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U62" s="2"/>
+      <c r="V62" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W62" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>0</v>
@@ -4656,32 +4726,33 @@
         <v>21</v>
       </c>
       <c r="O63" s="2"/>
-      <c r="P63" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q63" s="2">
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R63" s="2">
         <v>84</v>
       </c>
-      <c r="R63" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S63" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T63" s="2"/>
-      <c r="U63" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V63" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U63" s="2"/>
+      <c r="V63" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W63" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>0</v>
@@ -4716,32 +4787,33 @@
         <v>21</v>
       </c>
       <c r="O64" s="2"/>
-      <c r="P64" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q64" s="2">
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R64" s="2">
         <v>84</v>
       </c>
-      <c r="R64" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S64" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T64" s="2"/>
-      <c r="U64" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V64" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T64" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U64" s="2"/>
+      <c r="V64" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W64" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>0</v>
@@ -4776,32 +4848,33 @@
         <v>21</v>
       </c>
       <c r="O65" s="2"/>
-      <c r="P65" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q65" s="2">
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R65" s="2">
         <v>84</v>
       </c>
-      <c r="R65" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S65" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T65" s="2"/>
-      <c r="U65" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V65" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T65" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U65" s="2"/>
+      <c r="V65" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W65" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>0</v>
@@ -4836,32 +4909,33 @@
         <v>21</v>
       </c>
       <c r="O66" s="2"/>
-      <c r="P66" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q66" s="2">
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R66" s="2">
         <v>84</v>
       </c>
-      <c r="R66" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S66" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T66" s="2"/>
-      <c r="U66" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V66" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T66" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U66" s="2"/>
+      <c r="V66" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W66" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>0</v>
@@ -4896,32 +4970,33 @@
         <v>21</v>
       </c>
       <c r="O67" s="2"/>
-      <c r="P67" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q67" s="2">
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R67" s="2">
         <v>84</v>
       </c>
-      <c r="R67" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S67" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T67" s="2"/>
-      <c r="U67" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V67" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U67" s="2"/>
+      <c r="V67" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W67" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>68</v>
@@ -4954,32 +5029,33 @@
         <v>21</v>
       </c>
       <c r="O68" s="2"/>
-      <c r="P68" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q68" s="2">
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R68" s="2">
         <v>84</v>
       </c>
-      <c r="R68" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S68" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T68" s="2"/>
-      <c r="U68" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V68" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T68" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U68" s="2"/>
+      <c r="V68" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W68" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>68</v>
@@ -5012,32 +5088,33 @@
         <v>21</v>
       </c>
       <c r="O69" s="2"/>
-      <c r="P69" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q69" s="2">
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R69" s="2">
         <v>84</v>
       </c>
-      <c r="R69" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S69" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T69" s="2"/>
-      <c r="U69" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V69" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U69" s="2"/>
+      <c r="V69" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W69" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>68</v>
@@ -5070,32 +5147,33 @@
         <v>21</v>
       </c>
       <c r="O70" s="2"/>
-      <c r="P70" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q70" s="2">
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R70" s="2">
         <v>84</v>
       </c>
-      <c r="R70" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S70" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T70" s="2"/>
-      <c r="U70" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V70" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U70" s="2"/>
+      <c r="V70" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W70" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>68</v>
@@ -5128,32 +5206,33 @@
         <v>21</v>
       </c>
       <c r="O71" s="2"/>
-      <c r="P71" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q71" s="2">
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R71" s="2">
         <v>84</v>
       </c>
-      <c r="R71" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S71" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T71" s="2"/>
-      <c r="U71" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V71" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T71" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U71" s="2"/>
+      <c r="V71" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W71" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>68</v>
@@ -5186,32 +5265,33 @@
         <v>21</v>
       </c>
       <c r="O72" s="2"/>
-      <c r="P72" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q72" s="2">
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R72" s="2">
         <v>84</v>
       </c>
-      <c r="R72" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S72" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T72" s="2"/>
-      <c r="U72" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V72" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U72" s="2"/>
+      <c r="V72" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W72" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>68</v>
@@ -5244,32 +5324,33 @@
         <v>21</v>
       </c>
       <c r="O73" s="2"/>
-      <c r="P73" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q73" s="2">
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R73" s="2">
         <v>84</v>
       </c>
-      <c r="R73" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S73" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T73" s="2"/>
-      <c r="U73" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V73" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T73" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U73" s="2"/>
+      <c r="V73" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W73" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>0</v>
@@ -5302,32 +5383,33 @@
         <v>21</v>
       </c>
       <c r="O74" s="2"/>
-      <c r="P74" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q74" s="2">
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R74" s="2">
         <v>84</v>
       </c>
-      <c r="R74" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S74" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T74" s="2"/>
-      <c r="U74" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V74" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U74" s="2"/>
+      <c r="V74" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W74" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>0</v>
@@ -5360,32 +5442,33 @@
         <v>21</v>
       </c>
       <c r="O75" s="2"/>
-      <c r="P75" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q75" s="2">
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R75" s="2">
         <v>84</v>
       </c>
-      <c r="R75" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S75" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T75" s="2"/>
-      <c r="U75" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V75" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T75" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U75" s="2"/>
+      <c r="V75" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W75" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>0</v>
@@ -5418,32 +5501,33 @@
         <v>21</v>
       </c>
       <c r="O76" s="2"/>
-      <c r="P76" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q76" s="2">
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R76" s="2">
         <v>84</v>
       </c>
-      <c r="R76" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S76" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T76" s="2"/>
-      <c r="U76" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V76" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T76" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U76" s="2"/>
+      <c r="V76" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W76" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>0</v>
@@ -5476,32 +5560,33 @@
         <v>21</v>
       </c>
       <c r="O77" s="2"/>
-      <c r="P77" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q77" s="2">
+      <c r="P77" s="2"/>
+      <c r="Q77" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R77" s="2">
         <v>84</v>
       </c>
-      <c r="R77" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S77" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T77" s="2"/>
-      <c r="U77" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V77" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U77" s="2"/>
+      <c r="V77" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W77" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>0</v>
@@ -5534,32 +5619,33 @@
         <v>21</v>
       </c>
       <c r="O78" s="2"/>
-      <c r="P78" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q78" s="2">
+      <c r="P78" s="2"/>
+      <c r="Q78" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R78" s="2">
         <v>84</v>
       </c>
-      <c r="R78" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S78" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T78" s="2"/>
-      <c r="U78" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V78" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U78" s="2"/>
+      <c r="V78" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W78" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>0</v>
@@ -5592,27 +5678,28 @@
         <v>21</v>
       </c>
       <c r="O79" s="2"/>
-      <c r="P79" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q79" s="2">
+      <c r="P79" s="2"/>
+      <c r="Q79" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R79" s="2">
         <v>84</v>
       </c>
-      <c r="R79" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S79" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T79" s="2"/>
-      <c r="U79" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V79" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T79" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U79" s="2"/>
+      <c r="V79" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W79" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>122</v>
       </c>
@@ -5624,7 +5711,7 @@
         <v>45</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2" t="s">
@@ -5648,31 +5735,32 @@
         <v>21</v>
       </c>
       <c r="O80" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q80" s="2">
+      <c r="Q80" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R80" s="2">
         <v>84</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S80" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T80" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U80" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V80" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U80" s="2"/>
+      <c r="V80" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W80" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>125</v>
       </c>
@@ -5686,7 +5774,7 @@
         <v>45</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2" t="s">
@@ -5709,30 +5797,31 @@
       <c r="N81" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O81" s="2" t="s">
+      <c r="O81" s="2"/>
+      <c r="P81" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P81" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q81" s="2">
+      <c r="Q81" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R81" s="2">
         <v>84</v>
       </c>
-      <c r="R81" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S81" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T81" s="2"/>
-      <c r="U81" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V81" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T81" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U81" s="2"/>
+      <c r="V81" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W81" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
         <v>43</v>
       </c>
@@ -5744,7 +5833,7 @@
         <v>46</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2" t="s">
@@ -5768,31 +5857,32 @@
         <v>21</v>
       </c>
       <c r="O82" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P82" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P82" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q82" s="2">
+      <c r="Q82" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R82" s="2">
         <v>84</v>
       </c>
-      <c r="R82" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S82" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T82" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U82" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V82" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U82" s="2"/>
+      <c r="V82" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W82" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>45</v>
       </c>
@@ -5804,7 +5894,7 @@
         <v>47</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2" t="s">
@@ -5828,33 +5918,34 @@
         <v>21</v>
       </c>
       <c r="O83" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P83" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q83" s="2">
+      <c r="Q83" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R83" s="2">
         <v>84</v>
       </c>
-      <c r="R83" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S83" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T83" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U83" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V83" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U83" s="2"/>
+      <c r="V83" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W83" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" s="2" t="s">
@@ -5864,7 +5955,7 @@
         <v>48</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2" t="s">
@@ -5888,31 +5979,32 @@
         <v>21</v>
       </c>
       <c r="O84" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P84" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P84" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q84" s="2">
+      <c r="Q84" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R84" s="2">
         <v>84</v>
       </c>
-      <c r="R84" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S84" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T84" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U84" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V84" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U84" s="2"/>
+      <c r="V84" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W84" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>43</v>
       </c>
@@ -5924,7 +6016,7 @@
         <v>49</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2" t="s">
@@ -5948,31 +6040,32 @@
         <v>21</v>
       </c>
       <c r="O85" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P85" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P85" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q85" s="2">
+      <c r="Q85" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R85" s="2">
         <v>85</v>
       </c>
-      <c r="R85" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S85" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T85" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U85" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V85" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U85" s="2"/>
+      <c r="V85" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W85" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
         <v>43</v>
       </c>
@@ -5984,7 +6077,7 @@
         <v>50</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2" t="s">
@@ -6008,31 +6101,32 @@
         <v>21</v>
       </c>
       <c r="O86" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P86" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P86" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q86" s="2">
+      <c r="Q86" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R86" s="2">
         <v>85</v>
       </c>
-      <c r="R86" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S86" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T86" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U86" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V86" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U86" s="2"/>
+      <c r="V86" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W86" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>52</v>
       </c>
@@ -6046,7 +6140,7 @@
         <v>51</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2" t="s">
@@ -6070,31 +6164,32 @@
         <v>21</v>
       </c>
       <c r="O87" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P87" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P87" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q87" s="2">
+      <c r="Q87" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R87" s="2">
         <v>85</v>
       </c>
-      <c r="R87" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S87" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T87" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U87" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V87" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U87" s="2"/>
+      <c r="V87" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W87" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>122</v>
       </c>
@@ -6108,10 +6203,10 @@
         <v>52</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>27</v>
@@ -6134,31 +6229,32 @@
         <v>21</v>
       </c>
       <c r="O88" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P88" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P88" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q88" s="2">
+      <c r="Q88" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R88" s="2">
         <v>85</v>
       </c>
-      <c r="R88" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S88" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T88" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U88" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V88" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U88" s="2"/>
+      <c r="V88" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W88" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>122</v>
       </c>
@@ -6172,10 +6268,10 @@
         <v>52</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>27</v>
@@ -6198,31 +6294,32 @@
         <v>21</v>
       </c>
       <c r="O89" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P89" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P89" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q89" s="2">
+      <c r="Q89" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R89" s="2">
         <v>85</v>
       </c>
-      <c r="R89" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S89" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T89" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U89" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V89" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U89" s="2"/>
+      <c r="V89" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W89" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>122</v>
       </c>
@@ -6236,10 +6333,10 @@
         <v>53</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>27</v>
@@ -6262,31 +6359,32 @@
         <v>21</v>
       </c>
       <c r="O90" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P90" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P90" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q90" s="2">
+      <c r="Q90" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R90" s="2">
         <v>85</v>
       </c>
-      <c r="R90" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S90" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T90" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U90" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V90" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U90" s="2"/>
+      <c r="V90" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W90" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>122</v>
       </c>
@@ -6300,10 +6398,10 @@
         <v>53</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>27</v>
@@ -6326,31 +6424,32 @@
         <v>21</v>
       </c>
       <c r="O91" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P91" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P91" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q91" s="2">
+      <c r="Q91" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R91" s="2">
         <v>85</v>
       </c>
-      <c r="R91" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S91" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T91" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U91" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V91" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="92" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U91" s="2"/>
+      <c r="V91" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W91" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
         <v>43</v>
       </c>
@@ -6364,10 +6463,10 @@
         <v>54</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>27</v>
@@ -6387,32 +6486,33 @@
       <c r="N92" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="O92" s="4" t="s">
+      <c r="O92" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P92" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="P92" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q92" s="4">
+      <c r="Q92" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="R92" s="4">
         <v>85</v>
       </c>
-      <c r="R92" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S92" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T92" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U92" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V92" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="93" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U92" s="2"/>
+      <c r="V92" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W92" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
         <v>43</v>
       </c>
@@ -6426,10 +6526,10 @@
         <v>54</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G93" s="4" t="s">
         <v>27</v>
@@ -6449,32 +6549,33 @@
       <c r="N93" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="O93" s="4" t="s">
+      <c r="O93" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P93" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="P93" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q93" s="4">
+      <c r="Q93" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="R93" s="4">
         <v>85</v>
       </c>
-      <c r="R93" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S93" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T93" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U93" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V93" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U93" s="2"/>
+      <c r="V93" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W93" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>45</v>
       </c>
@@ -6488,10 +6589,10 @@
         <v>55</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>27</v>
@@ -6514,31 +6615,32 @@
         <v>21</v>
       </c>
       <c r="O94" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P94" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q94" s="2">
+      <c r="Q94" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R94" s="2">
         <v>85</v>
       </c>
-      <c r="R94" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S94" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T94" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U94" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V94" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U94" s="2"/>
+      <c r="V94" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W94" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>45</v>
       </c>
@@ -6552,10 +6654,10 @@
         <v>55</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>27</v>
@@ -6578,31 +6680,32 @@
         <v>21</v>
       </c>
       <c r="O95" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P95" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P95" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q95" s="2">
+      <c r="Q95" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R95" s="2">
         <v>85</v>
       </c>
-      <c r="R95" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S95" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T95" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U95" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V95" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U95" s="2"/>
+      <c r="V95" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W95" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>52</v>
       </c>
@@ -6616,10 +6719,10 @@
         <v>56</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>27</v>
@@ -6642,31 +6745,32 @@
         <v>21</v>
       </c>
       <c r="O96" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P96" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q96" s="2">
+      <c r="Q96" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R96" s="2">
         <v>85</v>
       </c>
-      <c r="R96" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S96" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T96" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U96" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V96" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U96" s="2"/>
+      <c r="V96" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W96" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>52</v>
       </c>
@@ -6680,10 +6784,10 @@
         <v>56</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>27</v>
@@ -6706,33 +6810,34 @@
         <v>21</v>
       </c>
       <c r="O97" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P97" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P97" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q97" s="2">
+      <c r="Q97" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R97" s="2">
         <v>85</v>
       </c>
-      <c r="R97" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S97" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T97" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U97" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V97" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U97" s="2"/>
+      <c r="V97" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W97" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>48</v>
@@ -6744,10 +6849,10 @@
         <v>57</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>27</v>
@@ -6770,33 +6875,34 @@
         <v>21</v>
       </c>
       <c r="O98" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P98" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P98" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q98" s="2">
+      <c r="Q98" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R98" s="2">
         <v>85</v>
       </c>
-      <c r="R98" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S98" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T98" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U98" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V98" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U98" s="2"/>
+      <c r="V98" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W98" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>48</v>
@@ -6808,10 +6914,10 @@
         <v>57</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>27</v>
@@ -6834,31 +6940,32 @@
         <v>21</v>
       </c>
       <c r="O99" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P99" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P99" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q99" s="2">
+      <c r="Q99" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R99" s="2">
         <v>85</v>
       </c>
-      <c r="R99" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S99" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T99" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U99" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V99" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U99" s="2"/>
+      <c r="V99" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W99" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>52</v>
       </c>
@@ -6870,10 +6977,10 @@
         <v>58</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>29</v>
@@ -6894,33 +7001,34 @@
         <v>21</v>
       </c>
       <c r="O100" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P100" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P100" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q100" s="2">
+      <c r="Q100" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R100" s="2">
         <v>85</v>
       </c>
-      <c r="R100" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S100" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T100" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U100" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V100" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U100" s="2"/>
+      <c r="V100" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W100" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" s="2" t="s">
@@ -6930,7 +7038,7 @@
         <v>59</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>121</v>
@@ -6957,34 +7065,35 @@
       <c r="N101" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O101" s="15" t="s">
+      <c r="O101" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P101" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="P101" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q101" s="2">
+      <c r="Q101" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R101" s="2">
         <v>85</v>
       </c>
-      <c r="R101" s="14" t="s">
+      <c r="S101" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="T101" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="S101" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="T101" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U101" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V101" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U101" s="2"/>
+      <c r="V101" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W101" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" s="2" t="s">
@@ -6994,7 +7103,7 @@
         <v>60</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>121</v>
@@ -7019,34 +7128,35 @@
       <c r="N102" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O102" s="15" t="s">
+      <c r="O102" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P102" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="P102" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q102" s="2">
+      <c r="Q102" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R102" s="2">
         <v>85</v>
       </c>
-      <c r="R102" s="14" t="s">
+      <c r="S102" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="T102" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="S102" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="T102" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U102" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V102" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U102" s="2"/>
+      <c r="V102" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W102" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B103" s="2"/>
       <c r="C103" s="2" t="s">
@@ -7056,7 +7166,7 @@
         <v>61</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>121</v>
@@ -7066,7 +7176,7 @@
       </c>
       <c r="H103" s="2"/>
       <c r="I103" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>73</v>
@@ -7083,34 +7193,35 @@
       <c r="N103" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O103" s="15" t="s">
+      <c r="O103" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P103" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="P103" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q103" s="2">
+      <c r="Q103" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R103" s="2">
         <v>85</v>
       </c>
-      <c r="R103" s="14" t="s">
+      <c r="S103" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="T103" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="S103" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="T103" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U103" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V103" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U103" s="2"/>
+      <c r="V103" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W103" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B104" s="2"/>
       <c r="C104" s="2" t="s">
@@ -7120,7 +7231,7 @@
         <v>62</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>121</v>
@@ -7130,7 +7241,7 @@
       </c>
       <c r="H104" s="2"/>
       <c r="I104" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>73</v>
@@ -7147,34 +7258,35 @@
       <c r="N104" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O104" s="15" t="s">
+      <c r="O104" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P104" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="P104" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q104" s="2">
+      <c r="Q104" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R104" s="2">
         <v>86</v>
       </c>
-      <c r="R104" s="14" t="s">
+      <c r="S104" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="T104" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="S104" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="T104" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U104" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V104" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U104" s="2"/>
+      <c r="V104" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W104" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" s="2" t="s">
@@ -7184,7 +7296,7 @@
         <v>63</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>121</v>
@@ -7194,10 +7306,10 @@
       </c>
       <c r="H105" s="2"/>
       <c r="I105" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K105" s="2" t="s">
         <v>6</v>
@@ -7211,34 +7323,35 @@
       <c r="N105" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O105" s="15" t="s">
+      <c r="O105" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P105" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="P105" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q105" s="2">
+      <c r="Q105" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R105" s="2">
         <v>86</v>
       </c>
-      <c r="R105" s="14" t="s">
+      <c r="S105" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="T105" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="S105" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="T105" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U105" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V105" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U105" s="2"/>
+      <c r="V105" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W105" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B106" s="2"/>
       <c r="C106" s="2" t="s">
@@ -7248,7 +7361,7 @@
         <v>64</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>121</v>
@@ -7273,34 +7386,35 @@
       <c r="N106" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O106" s="15" t="s">
+      <c r="O106" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P106" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="P106" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q106" s="2">
+      <c r="Q106" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R106" s="2">
         <v>86</v>
       </c>
-      <c r="R106" s="14" t="s">
+      <c r="S106" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="T106" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="S106" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="T106" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U106" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V106" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U106" s="2"/>
+      <c r="V106" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W106" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B107" s="2"/>
       <c r="C107" s="2" t="s">
@@ -7310,7 +7424,7 @@
         <v>65</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>121</v>
@@ -7335,34 +7449,35 @@
       <c r="N107" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O107" s="15" t="s">
+      <c r="O107" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P107" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="P107" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q107" s="2">
+      <c r="Q107" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R107" s="2">
         <v>86</v>
       </c>
-      <c r="R107" s="14" t="s">
+      <c r="S107" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="T107" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="S107" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="T107" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U107" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V107" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U107" s="2"/>
+      <c r="V107" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W107" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B108" s="2"/>
       <c r="C108" s="2" t="s">
@@ -7372,7 +7487,7 @@
         <v>66</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>121</v>
@@ -7399,34 +7514,35 @@
       <c r="N108" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O108" s="15" t="s">
+      <c r="O108" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P108" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="P108" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q108" s="2">
+      <c r="Q108" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R108" s="2">
         <v>86</v>
       </c>
-      <c r="R108" s="14" t="s">
+      <c r="S108" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="T108" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="S108" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="T108" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U108" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V108" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U108" s="2"/>
+      <c r="V108" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W108" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" s="2" t="s">
@@ -7436,7 +7552,7 @@
         <v>67</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>121</v>
@@ -7461,34 +7577,35 @@
       <c r="N109" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O109" s="15" t="s">
+      <c r="O109" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P109" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="P109" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q109" s="2">
+      <c r="Q109" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R109" s="2">
         <v>86</v>
       </c>
-      <c r="R109" s="14" t="s">
+      <c r="S109" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="T109" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="S109" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="T109" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U109" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V109" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U109" s="2"/>
+      <c r="V109" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W109" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B110" s="2"/>
       <c r="C110" s="2" t="s">
@@ -7498,7 +7615,7 @@
         <v>68</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>121</v>
@@ -7523,34 +7640,35 @@
       <c r="N110" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O110" s="15" t="s">
+      <c r="O110" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P110" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="P110" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q110" s="2">
+      <c r="Q110" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R110" s="2">
         <v>86</v>
       </c>
-      <c r="R110" s="14" t="s">
+      <c r="S110" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="T110" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="S110" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="T110" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U110" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V110" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U110" s="2"/>
+      <c r="V110" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W110" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B111" s="2"/>
       <c r="C111" s="2" t="s">
@@ -7560,7 +7678,7 @@
         <v>69</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>121</v>
@@ -7585,32 +7703,33 @@
       <c r="N111" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O111" s="15" t="s">
+      <c r="O111" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P111" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="P111" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q111" s="2">
+      <c r="Q111" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R111" s="2">
         <v>86</v>
       </c>
-      <c r="R111" s="14" t="s">
+      <c r="S111" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="T111" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="S111" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="T111" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U111" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V111" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U111" s="2"/>
+      <c r="V111" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W111" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>122</v>
       </c>
@@ -7624,7 +7743,7 @@
         <v>70</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2" t="s">
@@ -7648,31 +7767,32 @@
         <v>21</v>
       </c>
       <c r="O112" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P112" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P112" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q112" s="2">
+      <c r="Q112" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R112" s="2">
         <v>86</v>
       </c>
-      <c r="R112" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S112" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T112" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U112" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V112" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U112" s="2"/>
+      <c r="V112" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W112" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>122</v>
       </c>
@@ -7686,7 +7806,7 @@
         <v>70</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2" t="s">
@@ -7710,31 +7830,32 @@
         <v>21</v>
       </c>
       <c r="O113" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P113" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P113" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q113" s="2">
+      <c r="Q113" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R113" s="2">
         <v>86</v>
       </c>
-      <c r="R113" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S113" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T113" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U113" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V113" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U113" s="2"/>
+      <c r="V113" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W113" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>43</v>
       </c>
@@ -7746,7 +7867,7 @@
         <v>71</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2" t="s">
@@ -7770,31 +7891,32 @@
         <v>21</v>
       </c>
       <c r="O114" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P114" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P114" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q114" s="2">
+      <c r="Q114" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R114" s="2">
         <v>86</v>
       </c>
-      <c r="R114" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S114" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T114" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U114" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V114" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U114" s="2"/>
+      <c r="V114" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W114" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
         <v>43</v>
       </c>
@@ -7806,7 +7928,7 @@
         <v>71</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2" t="s">
@@ -7830,31 +7952,32 @@
         <v>21</v>
       </c>
       <c r="O115" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P115" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P115" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q115" s="2">
+      <c r="Q115" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R115" s="2">
         <v>86</v>
       </c>
-      <c r="R115" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S115" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T115" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U115" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V115" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U115" s="2"/>
+      <c r="V115" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W115" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>45</v>
       </c>
@@ -7868,7 +7991,7 @@
         <v>72</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2" t="s">
@@ -7892,31 +8015,32 @@
         <v>21</v>
       </c>
       <c r="O116" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P116" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P116" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q116" s="2">
+      <c r="Q116" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R116" s="2">
         <v>87</v>
       </c>
-      <c r="R116" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S116" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T116" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U116" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V116" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U116" s="2"/>
+      <c r="V116" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W116" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>45</v>
       </c>
@@ -7930,7 +8054,7 @@
         <v>72</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2" t="s">
@@ -7954,31 +8078,32 @@
         <v>21</v>
       </c>
       <c r="O117" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P117" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P117" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q117" s="2">
+      <c r="Q117" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R117" s="2">
         <v>87</v>
       </c>
-      <c r="R117" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S117" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T117" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U117" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V117" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U117" s="2"/>
+      <c r="V117" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W117" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>45</v>
       </c>
@@ -7992,7 +8117,7 @@
         <v>72</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2" t="s">
@@ -8016,31 +8141,32 @@
         <v>21</v>
       </c>
       <c r="O118" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P118" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P118" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q118" s="2">
+      <c r="Q118" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R118" s="2">
         <v>87</v>
       </c>
-      <c r="R118" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S118" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T118" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U118" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V118" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U118" s="2"/>
+      <c r="V118" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W118" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>45</v>
       </c>
@@ -8054,7 +8180,7 @@
         <v>72</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2" t="s">
@@ -8078,33 +8204,34 @@
         <v>21</v>
       </c>
       <c r="O119" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P119" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P119" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q119" s="2">
+      <c r="Q119" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R119" s="2">
         <v>87</v>
       </c>
-      <c r="R119" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S119" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T119" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U119" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V119" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U119" s="2"/>
+      <c r="V119" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W119" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>48</v>
@@ -8116,7 +8243,7 @@
         <v>73</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2" t="s">
@@ -8140,33 +8267,34 @@
         <v>21</v>
       </c>
       <c r="O120" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P120" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P120" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q120" s="2">
+      <c r="Q120" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R120" s="2">
         <v>87</v>
       </c>
-      <c r="R120" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S120" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T120" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U120" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V120" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U120" s="2"/>
+      <c r="V120" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W120" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>48</v>
@@ -8178,7 +8306,7 @@
         <v>73</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2" t="s">
@@ -8202,31 +8330,32 @@
         <v>21</v>
       </c>
       <c r="O121" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P121" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P121" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q121" s="2">
+      <c r="Q121" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R121" s="2">
         <v>87</v>
       </c>
-      <c r="R121" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S121" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T121" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U121" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V121" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U121" s="2"/>
+      <c r="V121" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W121" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>125</v>
       </c>
@@ -8240,7 +8369,7 @@
         <v>73</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2" t="s">
@@ -8263,30 +8392,31 @@
       <c r="N122" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O122" s="2" t="s">
-        <v>135</v>
-      </c>
+      <c r="O122" s="2"/>
       <c r="P122" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q122" s="2">
+        <v>134</v>
+      </c>
+      <c r="Q122" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R122" s="2">
         <v>87</v>
       </c>
-      <c r="R122" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S122" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T122" s="13"/>
-      <c r="U122" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V122" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T122" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U122" s="13"/>
+      <c r="V122" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W122" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>125</v>
       </c>
@@ -8300,7 +8430,7 @@
         <v>73</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F123" s="2"/>
       <c r="G123" s="2" t="s">
@@ -8323,34 +8453,39 @@
       <c r="N123" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O123" s="2" t="s">
-        <v>135</v>
-      </c>
+      <c r="O123" s="2"/>
       <c r="P123" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q123" s="2">
+        <v>134</v>
+      </c>
+      <c r="Q123" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R123" s="2">
         <v>87</v>
       </c>
-      <c r="R123" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="S123" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T123" s="13"/>
-      <c r="U123" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V123" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="T123" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U123" s="13"/>
+      <c r="V123" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="W123" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
       <c r="G124" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V123" xr:uid="{C316ADCA-0F97-4E34-A600-B1604EAF90B0}"/>
+  <autoFilter ref="A1:W123" xr:uid="{C316ADCA-0F97-4E34-A600-B1604EAF90B0}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W123">
+      <sortCondition ref="D1:D123"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
